--- a/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1939" uniqueCount="416">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-18T09:05:02+00:00</t>
+    <t>2025-04-24T12:12:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Appointment</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-appointment</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -329,13 +329,203 @@
 </t>
   </si>
   <si>
-    <t>Appointment.implicitRules</t>
+    <t>Appointment.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Appointment.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Appointment.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>Appointment.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>Appointment.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>Appointment.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:$this}
+</t>
+  </si>
+  <si>
+    <t>Slice based on the canonical url value</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>Appointment.meta.profile:fr-canonical</t>
+  </si>
+  <si>
+    <t>fr-canonical</t>
+  </si>
+  <si>
+    <t>Appointment.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>Appointment.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>Appointment.implicitRules</t>
+  </si>
+  <si>
     <t>A set of rules under which this content was created</t>
   </si>
   <si>
@@ -431,28 +621,33 @@
     <t>Appointment.extension</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>Appointment.extension:appointmentOperator</t>
+  </si>
+  <si>
+    <t>appointmentOperator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-appointment-operator}
 </t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
+    <t>FR Core Appointment Operator Extension</t>
+  </si>
+  <si>
+    <t>This extension adds the element appointmentOperator to the Appointment resource (operator of creation/update/cancel of the appointment | Cette extension ajoute l'élément appointmentOperator à la ressource Appointment (opérateur de création/modification/annulation du RDV)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
 </t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Appointment.extension:questionnaire</t>
@@ -471,15 +666,23 @@
     <t>Référence vers un ou plusieurs QuestionnaireResponse remplis dans le cadre de la préadmission.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
+    <t>Appointment.extension:consentements</t>
+  </si>
+  <si>
+    <t>consentements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-consent-fr-exntension}
 </t>
   </si>
   <si>
+    <t>Consentement lié au rendez-vous</t>
+  </si>
+  <si>
+    <t>Référence vers un ou plusieurs consentements donnés dans le cadre de la préadmission.</t>
+  </si>
+  <si>
     <t>Appointment.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
   </si>
   <si>
     <t>Extensions that cannot be ignored</t>
@@ -489,9 +692,6 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -576,15 +776,9 @@
     <t>The coded reason for the appointment being cancelled. This is often used in reporting/billing/futher processing to determine if further actions are required, or specific fees apply.</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
     <t>http://hl7.org/fhir/ValueSet/appointment-cancellation-reason</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Appointment.serviceCategory</t>
   </si>
   <si>
@@ -630,7 +824,7 @@
     <t>The specialty of a practitioner that would be required to perform the service requested in this appointment.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-specialty</t>
   </si>
   <si>
     <t>.performer.AssignedPerson.code</t>
@@ -736,10 +930,6 @@
     <t>Appointment.description</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
     <t>Shown on a subject line in a meeting request, or appointment list</t>
   </si>
   <si>
@@ -783,10 +973,6 @@
     <t>Appointment.start</t>
   </si>
   <si>
-    <t xml:space="preserve">instant
-</t>
-  </si>
-  <si>
     <t>When appointment is to take place</t>
   </si>
   <si>
@@ -851,7 +1037,7 @@
     <t>Appointment.slot</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Slot)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-slot)
 </t>
   </si>
   <si>
@@ -979,25 +1165,7 @@
     <t>Appointment.participant.id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t>Appointment.participant.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Appointment.participant.modifierExtension</t>
@@ -1033,9 +1201,6 @@
 This value SHALL be the same when creating an AppointmentResponse so that they can be matched, and subsequently update the Appointment.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
     <t>Role of participant in encounter.</t>
   </si>
   <si>
@@ -1051,7 +1216,7 @@
     <t>Appointment.participant.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole|RelatedPerson|Device|HealthcareService|Location)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
 </t>
   </si>
   <si>
@@ -1457,12 +1622,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO41"/>
+  <dimension ref="A1:AO52"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="34.8671875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="36.921875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="34.8671875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.6953125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="18.01171875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1484,11 +1649,11 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="43.28515625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="48.55859375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.66796875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1996,10 +2161,10 @@
         <v>79</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>104</v>
@@ -2010,9 +2175,7 @@
       <c r="M5" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="N5" t="s" s="2">
-        <v>107</v>
-      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>79</v>
@@ -2061,7 +2224,7 @@
         <v>79</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
@@ -2073,13 +2236,13 @@
         <v>79</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="AM5" t="s" s="2">
         <v>79</v>
@@ -2100,14 +2263,14 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>79</v>
@@ -2119,16 +2282,16 @@
         <v>79</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2154,49 +2317,49 @@
         <v>79</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="Y6" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB6" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AC6" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AD6" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="AM6" t="s" s="2">
         <v>79</v>
@@ -2210,14 +2373,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>119</v>
+        <v>79</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2233,10 +2396,10 @@
         <v>79</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>120</v>
+        <v>92</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>121</v>
@@ -2313,7 +2476,7 @@
         <v>79</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>125</v>
+        <v>79</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>79</v>
@@ -2327,21 +2490,21 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>127</v>
+        <v>79</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>79</v>
@@ -2350,19 +2513,19 @@
         <v>79</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="M8" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2412,25 +2575,25 @@
         <v>79</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>133</v>
+        <v>79</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>79</v>
@@ -2444,10 +2607,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2458,7 +2621,7 @@
         <v>80</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>79</v>
@@ -2467,18 +2630,20 @@
         <v>79</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M9" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="N9" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="L9" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>79</v>
@@ -2515,29 +2680,31 @@
         <v>79</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>79</v>
@@ -2557,14 +2724,12 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>79</v>
       </c>
@@ -2582,18 +2747,20 @@
         <v>79</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N10" s="2"/>
+        <v>140</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>79</v>
@@ -2630,19 +2797,19 @@
         <v>79</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>79</v>
+        <v>142</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>79</v>
+        <v>143</v>
       </c>
       <c r="AD10" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -2651,10 +2818,10 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>147</v>
+        <v>79</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>79</v>
@@ -2674,46 +2841,46 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="D11" t="s" s="2">
-        <v>149</v>
+        <v>79</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I11" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J11" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="J11" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="K11" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>153</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>79</v>
       </c>
@@ -2722,7 +2889,7 @@
         <v>79</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>79</v>
@@ -2761,7 +2928,7 @@
         <v>79</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -2773,13 +2940,13 @@
         <v>79</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>133</v>
+        <v>79</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>79</v>
@@ -2793,10 +2960,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2819,15 +2986,17 @@
         <v>91</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>150</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>79</v>
@@ -2852,13 +3021,13 @@
         <v>79</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>79</v>
+        <v>153</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>79</v>
+        <v>154</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>79</v>
@@ -2891,27 +3060,27 @@
         <v>102</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>160</v>
+        <v>79</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>161</v>
+        <v>79</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>162</v>
+        <v>79</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>163</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2919,31 +3088,31 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2969,13 +3138,13 @@
         <v>79</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>79</v>
@@ -2993,13 +3162,13 @@
         <v>79</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>79</v>
@@ -3008,27 +3177,27 @@
         <v>102</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>171</v>
+        <v>79</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>172</v>
+        <v>79</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>173</v>
+        <v>79</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>175</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3045,21 +3214,23 @@
         <v>79</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>177</v>
+        <v>132</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N14" s="2"/>
+        <v>166</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>167</v>
+      </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>79</v>
@@ -3084,11 +3255,13 @@
         <v>79</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="Y14" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z14" t="s" s="2">
-        <v>181</v>
+        <v>79</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>79</v>
@@ -3106,7 +3279,7 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3124,7 +3297,7 @@
         <v>79</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>182</v>
+        <v>79</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>79</v>
@@ -3138,10 +3311,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3152,7 +3325,7 @@
         <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>79</v>
@@ -3161,18 +3334,20 @@
         <v>79</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>172</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>79</v>
@@ -3197,11 +3372,13 @@
         <v>79</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="Y15" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="Z15" t="s" s="2">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>79</v>
@@ -3219,13 +3396,13 @@
         <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>79</v>
@@ -3237,10 +3414,10 @@
         <v>79</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>187</v>
+        <v>79</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>188</v>
+        <v>79</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>79</v>
@@ -3251,21 +3428,21 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>79</v>
+        <v>179</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>79</v>
@@ -3274,19 +3451,19 @@
         <v>79</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3312,11 +3489,13 @@
         <v>79</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="Y16" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z16" t="s" s="2">
-        <v>193</v>
+        <v>79</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>79</v>
@@ -3334,13 +3513,13 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>79</v>
@@ -3349,10 +3528,10 @@
         <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>194</v>
+        <v>79</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>79</v>
@@ -3366,14 +3545,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>79</v>
+        <v>187</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3389,18 +3568,20 @@
         <v>79</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>191</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>79</v>
@@ -3425,11 +3606,13 @@
         <v>79</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="Y17" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z17" t="s" s="2">
-        <v>198</v>
+        <v>79</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>79</v>
@@ -3447,7 +3630,7 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3459,19 +3642,19 @@
         <v>79</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>200</v>
+        <v>79</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>79</v>
@@ -3479,10 +3662,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3493,7 +3676,7 @@
         <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>79</v>
@@ -3502,16 +3685,16 @@
         <v>79</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>177</v>
+        <v>111</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3538,66 +3721,68 @@
         <v>79</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="Y18" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z18" t="s" s="2">
-        <v>204</v>
+        <v>79</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="AC18" s="2"/>
       <c r="AD18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>205</v>
+        <v>79</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>206</v>
+        <v>79</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>207</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="D19" t="s" s="2">
         <v>79</v>
       </c>
@@ -3606,7 +3791,7 @@
         <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>79</v>
@@ -3615,16 +3800,16 @@
         <v>79</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3651,13 +3836,13 @@
         <v>79</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>211</v>
+        <v>79</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>212</v>
+        <v>79</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>79</v>
@@ -3675,7 +3860,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -3684,16 +3869,16 @@
         <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>79</v>
+        <v>203</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>213</v>
+        <v>79</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>214</v>
+        <v>79</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>79</v>
@@ -3702,17 +3887,19 @@
         <v>79</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>215</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="D20" t="s" s="2">
         <v>79</v>
       </c>
@@ -3733,13 +3920,13 @@
         <v>79</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3790,7 +3977,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>216</v>
+        <v>197</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -3802,13 +3989,13 @@
         <v>79</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>220</v>
+        <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>221</v>
+        <v>79</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>79</v>
@@ -3822,12 +4009,14 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="C21" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="D21" t="s" s="2">
         <v>79</v>
       </c>
@@ -3836,7 +4025,7 @@
         <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>79</v>
@@ -3848,17 +4037,15 @@
         <v>79</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>79</v>
@@ -3907,74 +4094,78 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>222</v>
+        <v>197</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>227</v>
+        <v>79</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>228</v>
+        <v>79</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>229</v>
+        <v>79</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>200</v>
+        <v>79</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>230</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>232</v>
+        <v>111</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>79</v>
       </c>
@@ -4022,42 +4213,42 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>235</v>
+        <v>193</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>236</v>
+        <v>79</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>237</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>238</v>
+        <v>219</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>238</v>
+        <v>219</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4077,16 +4268,16 @@
         <v>79</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4137,7 +4328,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>238</v>
+        <v>219</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4152,27 +4343,27 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>242</v>
+        <v>223</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>244</v>
+        <v>225</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>79</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4180,7 +4371,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>90</v>
@@ -4189,21 +4380,23 @@
         <v>79</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>247</v>
+        <v>170</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>248</v>
+        <v>229</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>79</v>
@@ -4228,13 +4421,13 @@
         <v>79</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>79</v>
+        <v>232</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>79</v>
+        <v>233</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>79</v>
+        <v>234</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>79</v>
@@ -4252,10 +4445,10 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>90</v>
@@ -4267,27 +4460,27 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>254</v>
+        <v>239</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4310,13 +4503,13 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4343,13 +4536,11 @@
         <v>79</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>79</v>
+        <v>244</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>79</v>
@@ -4367,7 +4558,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4382,27 +4573,27 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>250</v>
+        <v>79</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>258</v>
+        <v>108</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>259</v>
+        <v>79</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>260</v>
+        <v>79</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>261</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4413,7 +4604,7 @@
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>79</v>
@@ -4422,16 +4613,16 @@
         <v>79</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4458,13 +4649,11 @@
         <v>79</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>79</v>
+        <v>248</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>79</v>
@@ -4482,13 +4671,13 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>79</v>
@@ -4497,13 +4686,13 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>79</v>
@@ -4514,10 +4703,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4537,18 +4726,20 @@
         <v>79</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>269</v>
+        <v>241</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>79</v>
@@ -4573,13 +4764,11 @@
         <v>79</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>79</v>
+        <v>255</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>79</v>
@@ -4597,7 +4786,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4612,10 +4801,10 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>79</v>
+        <v>256</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>272</v>
+        <v>249</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>79</v>
@@ -4629,10 +4818,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4643,7 +4832,7 @@
         <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>79</v>
@@ -4652,20 +4841,18 @@
         <v>79</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>274</v>
+        <v>241</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>275</v>
+        <v>258</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>79</v>
@@ -4690,13 +4877,11 @@
         <v>79</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>79</v>
+        <v>260</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>79</v>
@@ -4714,13 +4899,13 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>79</v>
@@ -4729,16 +4914,16 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>278</v>
+        <v>79</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>280</v>
+        <v>79</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>79</v>
+        <v>262</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>79</v>
@@ -4746,10 +4931,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4769,20 +4954,18 @@
         <v>79</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>284</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>79</v>
@@ -4807,13 +4990,11 @@
         <v>79</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>79</v>
+        <v>266</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>79</v>
@@ -4831,7 +5012,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -4846,27 +5027,27 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>285</v>
+        <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>287</v>
+        <v>268</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>237</v>
+        <v>269</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4877,7 +5058,7 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>79</v>
@@ -4886,16 +5067,16 @@
         <v>79</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4922,13 +5103,13 @@
         <v>79</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>79</v>
+        <v>174</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>79</v>
+        <v>273</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>79</v>
+        <v>274</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>79</v>
@@ -4946,13 +5127,13 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>79</v>
@@ -4961,31 +5142,31 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>79</v>
+        <v>275</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>291</v>
+        <v>79</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>237</v>
+        <v>277</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>293</v>
+        <v>79</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5004,13 +5185,13 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5061,7 +5242,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5076,10 +5257,10 @@
         <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>79</v>
@@ -5093,10 +5274,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5104,11 +5285,11 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G32" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="G32" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="H32" t="s" s="2">
         <v>79</v>
       </c>
@@ -5119,15 +5300,17 @@
         <v>79</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>79</v>
@@ -5176,42 +5359,42 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="AG32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH32" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="AH32" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>303</v>
+        <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>79</v>
+        <v>262</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>307</v>
+        <v>292</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>308</v>
+        <v>293</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>308</v>
+        <v>293</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5234,13 +5417,13 @@
         <v>79</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>232</v>
+        <v>104</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5291,7 +5474,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>311</v>
+        <v>293</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5303,34 +5486,34 @@
         <v>79</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>182</v>
+        <v>296</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>79</v>
+        <v>297</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>79</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>149</v>
+        <v>79</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5349,17 +5532,15 @@
         <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>135</v>
+        <v>300</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>79</v>
@@ -5408,7 +5589,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>315</v>
+        <v>299</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5420,19 +5601,19 @@
         <v>79</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>79</v>
+        <v>303</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>182</v>
+        <v>304</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>79</v>
+        <v>305</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>79</v>
+        <v>306</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>79</v>
@@ -5440,46 +5621,42 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>317</v>
+        <v>79</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J35" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>153</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>79</v>
       </c>
@@ -5527,42 +5704,42 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>79</v>
+        <v>310</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>133</v>
+        <v>311</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>79</v>
+        <v>312</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>79</v>
+        <v>313</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>79</v>
+        <v>314</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5573,7 +5750,7 @@
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>79</v>
@@ -5585,17 +5762,15 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>177</v>
+        <v>126</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>324</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>79</v>
@@ -5620,13 +5795,13 @@
         <v>79</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>325</v>
+        <v>79</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>326</v>
+        <v>79</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>327</v>
+        <v>79</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>79</v>
@@ -5644,13 +5819,13 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>79</v>
@@ -5659,27 +5834,27 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>79</v>
+        <v>310</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>182</v>
+        <v>319</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>79</v>
+        <v>320</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>329</v>
+        <v>321</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5699,16 +5874,16 @@
         <v>79</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5759,7 +5934,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5774,27 +5949,27 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>79</v>
+        <v>310</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>336</v>
+        <v>79</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>337</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5805,7 +5980,7 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>79</v>
@@ -5814,16 +5989,16 @@
         <v>79</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>110</v>
+        <v>329</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5850,13 +6025,13 @@
         <v>79</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>341</v>
+        <v>79</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>342</v>
+        <v>79</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>79</v>
@@ -5874,13 +6049,13 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>79</v>
@@ -5892,10 +6067,10 @@
         <v>79</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>344</v>
+        <v>79</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>79</v>
@@ -5906,10 +6081,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5917,7 +6092,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>90</v>
@@ -5929,18 +6104,20 @@
         <v>79</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>110</v>
+        <v>334</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>337</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>79</v>
@@ -5965,13 +6142,13 @@
         <v>79</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>348</v>
+        <v>79</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>349</v>
+        <v>79</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>79</v>
@@ -5989,10 +6166,10 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>90</v>
@@ -6004,27 +6181,27 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>79</v>
+        <v>338</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>352</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6047,15 +6224,17 @@
         <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>354</v>
+        <v>104</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>343</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>344</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>79</v>
@@ -6104,7 +6283,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6119,27 +6298,27 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>79</v>
+        <v>345</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>182</v>
+        <v>346</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>79</v>
+        <v>347</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>79</v>
+        <v>298</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6150,7 +6329,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>79</v>
@@ -6162,17 +6341,15 @@
         <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>354</v>
+        <v>104</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>360</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>79</v>
@@ -6221,13 +6398,13 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>79</v>
@@ -6236,19 +6413,1294 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>250</v>
+        <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO41" t="s" s="2">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO42" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="AM41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO41" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>362</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
+      <c r="P43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO43" t="s" s="2">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+      <c r="P44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO44" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O45" s="2"/>
+      <c r="P45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO45" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="P46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO46" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="O47" s="2"/>
+      <c r="P47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO47" t="s" s="2">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
+      <c r="P48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AO48" t="s" s="2">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO49" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO50" t="s" s="2">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
+      <c r="P51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO51" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="O52" s="2"/>
+      <c r="P52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO52" t="s" s="2">
+        <v>415</v>
       </c>
     </row>
   </sheetData>

--- a/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:12:45+00:00</t>
+    <t>2025-04-24T12:14:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:14:49+00:00</t>
+    <t>2025-04-24T12:53:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:53:37+00:00</t>
+    <t>2025-04-25T09:56:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1216,7 +1216,7 @@
     <t>Appointment.participant.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-ins)
 </t>
   </si>
   <si>

--- a/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-appointment-fr</t>
+    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/preadmission-appointment-fr</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T09:56:34+00:00</t>
+    <t>2025-04-25T14:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -656,7 +656,7 @@
     <t>questionnaire</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/appointment-questionnaire-response}
+    <t xml:space="preserve">Extension {https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/appointment-questionnaire-response}
 </t>
   </si>
   <si>
@@ -672,7 +672,7 @@
     <t>consentements</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-consent-fr-exntension}
+    <t xml:space="preserve">Extension {https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/preadmission-consent-fr-exntension}
 </t>
   </si>
   <si>
@@ -1635,7 +1635,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="81.25390625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="100.99609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T14:29:23+00:00</t>
+    <t>2025-04-25T16:50:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1216,7 +1216,7 @@
     <t>Appointment.participant.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-ins)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
 </t>
   </si>
   <si>
@@ -1635,7 +1635,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="100.99609375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="103.15625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/preadmission-appointment-fr</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-appointment-fr</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T16:50:14+00:00</t>
+    <t>2025-04-28T06:55:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -656,7 +656,7 @@
     <t>questionnaire</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/appointment-questionnaire-response}
+    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/appointment-questionnaire-response}
 </t>
   </si>
   <si>
@@ -672,7 +672,7 @@
     <t>consentements</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/preadmission-consent-fr-exntension}
+    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-consent-fr-exntension}
 </t>
   </si>
   <si>

--- a/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T06:55:35+00:00</t>
+    <t>2025-04-28T10:41:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T10:41:02+00:00</t>
+    <t>2025-05-05T08:51:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -672,7 +672,7 @@
     <t>consentements</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-consent-fr-exntension}
+    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-consent-fr-extension}
 </t>
   </si>
   <si>
@@ -1216,7 +1216,7 @@
     <t>Appointment.participant.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner)
 </t>
   </si>
   <si>
@@ -1635,7 +1635,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="103.15625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="106.7109375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-05T08:51:40+00:00</t>
+    <t>2025-05-06T13:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T13:54:59+00:00</t>
+    <t>2025-05-14T09:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Interop'Santé (http://interopsante.org/)</t>
   </si>
   <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T09:00:47+00:00</t>
+    <t>2025-05-22T16:12:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil FHIR pour un rendez-vous de préadmission</t>
+    <t>Profil Appointment pour un rendez-vous de préadmission</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -676,10 +676,10 @@
 </t>
   </si>
   <si>
-    <t>Consentement lié au rendez-vous</t>
-  </si>
-  <si>
-    <t>Référence vers un ou plusieurs consentements donnés dans le cadre de la préadmission.</t>
+    <t>Consentements</t>
+  </si>
+  <si>
+    <t>Consentement lié à la préadmission</t>
   </si>
   <si>
     <t>Appointment.modifierExtension</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-22T16:12:30+00:00</t>
+    <t>2025-05-26T06:59:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-26T06:59:47+00:00</t>
+    <t>2025-06-02T15:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1939" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1902" uniqueCount="411">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-02T15:02:23+00:00</t>
+    <t>2025-10-22T09:09:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -664,22 +664,6 @@
   </si>
   <si>
     <t>Référence vers un ou plusieurs QuestionnaireResponse remplis dans le cadre de la préadmission.</t>
-  </si>
-  <si>
-    <t>Appointment.extension:consentements</t>
-  </si>
-  <si>
-    <t>consentements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-consent-fr-extension}
-</t>
-  </si>
-  <si>
-    <t>Consentements</t>
-  </si>
-  <si>
-    <t>Consentement lié à la préadmission</t>
   </si>
   <si>
     <t>Appointment.modifierExtension</t>
@@ -1622,7 +1606,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO52"/>
+  <dimension ref="A1:AO51"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="36.921875" customWidth="true" bestFit="true"/>
@@ -4012,13 +3996,11 @@
         <v>209</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="C21" t="s" s="2">
-        <v>210</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4031,22 +4013,26 @@
         <v>79</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="N21" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O21" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="M21" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>79</v>
       </c>
@@ -4094,7 +4080,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4112,7 +4098,7 @@
         <v>79</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>79</v>
+        <v>193</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>79</v>
@@ -4133,7 +4119,7 @@
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4146,26 +4132,22 @@
         <v>79</v>
       </c>
       <c r="I22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J22" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="J22" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="K22" t="s" s="2">
-        <v>111</v>
+        <v>215</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O22" t="s" s="2">
         <v>217</v>
       </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>79</v>
       </c>
@@ -4213,7 +4195,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4225,30 +4207,30 @@
         <v>79</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>79</v>
+        <v>218</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>193</v>
+        <v>219</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>79</v>
+        <v>220</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>79</v>
+        <v>221</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>79</v>
+        <v>222</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4256,30 +4238,32 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>220</v>
+        <v>170</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>225</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>79</v>
@@ -4304,13 +4288,13 @@
         <v>79</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>79</v>
+        <v>227</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>79</v>
+        <v>228</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>79</v>
+        <v>229</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>79</v>
@@ -4328,13 +4312,13 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>79</v>
@@ -4343,27 +4327,27 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4371,7 +4355,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>90</v>
@@ -4380,23 +4364,21 @@
         <v>79</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>170</v>
+        <v>236</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>79</v>
@@ -4421,13 +4403,11 @@
         <v>79</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>79</v>
@@ -4445,10 +4425,10 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>90</v>
@@ -4460,19 +4440,19 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>235</v>
+        <v>79</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>236</v>
+        <v>108</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>237</v>
+        <v>79</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>238</v>
+        <v>79</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>239</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25">
@@ -4491,7 +4471,7 @@
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>79</v>
@@ -4503,13 +4483,13 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4540,7 +4520,7 @@
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>79</v>
@@ -4564,7 +4544,7 @@
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>79</v>
@@ -4576,10 +4556,10 @@
         <v>79</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>108</v>
+        <v>244</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>79</v>
+        <v>245</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>79</v>
@@ -4590,10 +4570,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4616,15 +4596,17 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>79</v>
@@ -4653,7 +4635,7 @@
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>79</v>
@@ -4671,7 +4653,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4686,13 +4668,13 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>79</v>
+        <v>251</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>250</v>
+        <v>79</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>79</v>
@@ -4703,10 +4685,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4729,17 +4711,15 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="N27" t="s" s="2">
         <v>254</v>
       </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>79</v>
@@ -4764,7 +4744,7 @@
         <v>79</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>160</v>
+        <v>227</v>
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
@@ -4786,7 +4766,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4801,16 +4781,16 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="AL27" t="s" s="2">
-        <v>249</v>
-      </c>
       <c r="AM27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>79</v>
+        <v>257</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>79</v>
@@ -4818,10 +4798,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4832,7 +4812,7 @@
         <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>79</v>
@@ -4844,13 +4824,13 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4877,11 +4857,11 @@
         <v>79</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>232</v>
+        <v>174</v>
       </c>
       <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>79</v>
@@ -4899,13 +4879,13 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>79</v>
@@ -4917,24 +4897,24 @@
         <v>79</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>79</v>
+        <v>263</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>262</v>
+        <v>79</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>79</v>
+        <v>264</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4945,7 +4925,7 @@
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>79</v>
@@ -4957,13 +4937,13 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4992,9 +4972,11 @@
       <c r="X29" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="Y29" s="2"/>
+      <c r="Y29" t="s" s="2">
+        <v>268</v>
+      </c>
       <c r="Z29" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>79</v>
@@ -5012,13 +4994,13 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>79</v>
@@ -5027,27 +5009,27 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>79</v>
+        <v>270</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>268</v>
+        <v>79</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5067,16 +5049,16 @@
         <v>79</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>241</v>
+        <v>274</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5103,31 +5085,31 @@
         <v>79</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="Y30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5142,10 +5124,10 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>79</v>
@@ -5154,15 +5136,15 @@
         <v>79</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>277</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5173,7 +5155,7 @@
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>79</v>
@@ -5185,15 +5167,17 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>79</v>
@@ -5242,13 +5226,13 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>79</v>
@@ -5257,27 +5241,27 @@
         <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>79</v>
+        <v>286</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>79</v>
+        <v>257</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>79</v>
+        <v>287</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5300,17 +5284,15 @@
         <v>79</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>285</v>
+        <v>104</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>79</v>
@@ -5359,7 +5341,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5374,27 +5356,27 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>289</v>
+        <v>79</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>262</v>
+        <v>79</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5405,7 +5387,7 @@
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>79</v>
@@ -5417,13 +5399,13 @@
         <v>79</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>104</v>
+        <v>295</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5474,13 +5456,13 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>79</v>
@@ -5489,27 +5471,27 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>79</v>
+        <v>298</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>79</v>
+        <v>301</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>298</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5520,7 +5502,7 @@
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>79</v>
@@ -5529,16 +5511,16 @@
         <v>79</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>300</v>
+        <v>126</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5589,13 +5571,13 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>79</v>
@@ -5604,27 +5586,27 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>79</v>
+        <v>309</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5650,10 +5632,10 @@
         <v>126</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5704,7 +5686,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5719,27 +5701,27 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5759,16 +5741,16 @@
         <v>79</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>126</v>
+        <v>318</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5819,7 +5801,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5834,27 +5816,27 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>320</v>
+        <v>79</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>321</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5865,7 +5847,7 @@
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>79</v>
@@ -5877,13 +5859,13 @@
         <v>79</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5934,13 +5916,13 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>79</v>
@@ -5949,13 +5931,13 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>310</v>
+        <v>79</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>327</v>
+        <v>79</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>79</v>
@@ -5980,7 +5962,7 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>79</v>
@@ -6000,7 +5982,9 @@
       <c r="M38" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="N38" s="2"/>
+      <c r="N38" t="s" s="2">
+        <v>332</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>79</v>
@@ -6055,7 +6039,7 @@
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>79</v>
@@ -6064,13 +6048,13 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>79</v>
+        <v>333</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>79</v>
+        <v>335</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>79</v>
@@ -6081,10 +6065,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6107,16 +6091,16 @@
         <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>334</v>
+        <v>104</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6166,7 +6150,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6181,27 +6165,27 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>79</v>
+        <v>293</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6227,14 +6211,12 @@
         <v>104</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>344</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>79</v>
@@ -6283,7 +6265,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6298,38 +6280,38 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>345</v>
+        <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="AM40" t="s" s="2">
-        <v>347</v>
-      </c>
       <c r="AN40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>79</v>
+        <v>348</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>79</v>
@@ -6341,13 +6323,13 @@
         <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>104</v>
+        <v>349</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6398,13 +6380,13 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>79</v>
@@ -6413,35 +6395,35 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>79</v>
+        <v>352</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>351</v>
+        <v>79</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>298</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>353</v>
+        <v>79</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>81</v>
@@ -6456,13 +6438,13 @@
         <v>79</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6513,10 +6495,10 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>81</v>
@@ -6525,30 +6507,30 @@
         <v>79</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>102</v>
+        <v>358</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>79</v>
+        <v>361</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>79</v>
+        <v>362</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6556,11 +6538,11 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G43" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="G43" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="H43" t="s" s="2">
         <v>79</v>
       </c>
@@ -6571,13 +6553,13 @@
         <v>79</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>360</v>
+        <v>104</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>361</v>
+        <v>105</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>362</v>
+        <v>106</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6628,53 +6610,53 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>359</v>
+        <v>107</v>
       </c>
       <c r="AG43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH43" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="AH43" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>363</v>
+        <v>79</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>364</v>
+        <v>79</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>365</v>
+        <v>108</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>366</v>
+        <v>79</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>367</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>79</v>
@@ -6686,15 +6668,17 @@
         <v>79</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -6743,19 +6727,19 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>79</v>
@@ -6775,14 +6759,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>110</v>
+        <v>366</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6795,24 +6779,26 @@
         <v>79</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
         <v>111</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>112</v>
+        <v>367</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>113</v>
+        <v>368</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="O45" s="2"/>
+      <c r="O45" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>79</v>
       </c>
@@ -6860,7 +6846,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>118</v>
+        <v>369</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6878,7 +6864,7 @@
         <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>108</v>
+        <v>193</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>79</v>
@@ -6899,7 +6885,7 @@
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>371</v>
+        <v>79</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6912,26 +6898,24 @@
         <v>79</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J46" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>111</v>
+        <v>236</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="N46" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>217</v>
-      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>79</v>
       </c>
@@ -6955,13 +6939,13 @@
         <v>79</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>79</v>
+        <v>374</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>79</v>
+        <v>375</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>79</v>
@@ -6979,7 +6963,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6991,30 +6975,30 @@
         <v>79</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>193</v>
+        <v>376</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>79</v>
+        <v>377</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7025,7 +7009,7 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>79</v>
@@ -7037,17 +7021,15 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>241</v>
+        <v>379</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>378</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>79</v>
@@ -7072,13 +7054,13 @@
         <v>79</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>152</v>
+        <v>79</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>379</v>
+        <v>79</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>380</v>
+        <v>79</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>79</v>
@@ -7096,13 +7078,13 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>79</v>
@@ -7114,24 +7096,24 @@
         <v>79</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>108</v>
+        <v>383</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>79</v>
+        <v>384</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7154,13 +7136,13 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>384</v>
+        <v>170</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7187,13 +7169,13 @@
         <v>79</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>79</v>
+        <v>227</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>79</v>
+        <v>389</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>79</v>
+        <v>390</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>79</v>
@@ -7211,7 +7193,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7229,24 +7211,24 @@
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>389</v>
+        <v>79</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>390</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7254,7 +7236,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>90</v>
@@ -7272,10 +7254,10 @@
         <v>170</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7302,13 +7284,13 @@
         <v>79</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>79</v>
@@ -7326,10 +7308,10 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>90</v>
@@ -7344,24 +7326,24 @@
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>79</v>
+        <v>400</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7369,7 +7351,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>90</v>
@@ -7381,16 +7363,16 @@
         <v>79</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>170</v>
+        <v>402</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7417,34 +7399,34 @@
         <v>79</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>232</v>
+        <v>79</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF50" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="Z50" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>398</v>
-      </c>
       <c r="AG50" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>90</v>
@@ -7459,24 +7441,24 @@
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>403</v>
+        <v>108</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>404</v>
+        <v>79</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>405</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7487,7 +7469,7 @@
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>79</v>
@@ -7499,15 +7481,17 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="M51" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>79</v>
@@ -7556,13 +7540,13 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>79</v>
@@ -7571,10 +7555,10 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>79</v>
+        <v>305</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>108</v>
+        <v>409</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
@@ -7583,124 +7567,7 @@
         <v>79</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="C52" s="2"/>
-      <c r="D52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E52" s="2"/>
-      <c r="F52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G52" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K52" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="O52" s="2"/>
-      <c r="P52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q52" s="2"/>
-      <c r="R52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK52" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>415</v>
       </c>
     </row>
   </sheetData>

--- a/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-22T09:09:51+00:00</t>
+    <t>2025-10-28T10:00:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1200,7 +1200,7 @@
     <t>Appointment.participant.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-ins|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner)
 </t>
   </si>
   <si>
@@ -1619,7 +1619,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="106.7109375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="156.30078125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-28T10:00:18+00:00</t>
+    <t>2025-11-19T09:47:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-19T09:47:12+00:00</t>
+    <t>2026-01-14T12:51:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1902" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1865" uniqueCount="406">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-14T12:51:21+00:00</t>
+    <t>2026-02-24T09:27:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -648,22 +648,6 @@
   <si>
     <t xml:space="preserve">ele-1
 </t>
-  </si>
-  <si>
-    <t>Appointment.extension:questionnaire</t>
-  </si>
-  <si>
-    <t>questionnaire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/appointment-questionnaire-response}
-</t>
-  </si>
-  <si>
-    <t>Questionnaire lié au rendez-vous</t>
-  </si>
-  <si>
-    <t>Référence vers un ou plusieurs QuestionnaireResponse remplis dans le cadre de la préadmission.</t>
   </si>
   <si>
     <t>Appointment.modifierExtension</t>
@@ -1606,7 +1590,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO51"/>
+  <dimension ref="A1:AO50"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="36.921875" customWidth="true" bestFit="true"/>
@@ -3879,13 +3863,11 @@
         <v>204</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>205</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3898,22 +3880,26 @@
         <v>79</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="N20" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O20" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="M20" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>79</v>
       </c>
@@ -3961,7 +3947,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -3979,7 +3965,7 @@
         <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>79</v>
+        <v>193</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>79</v>
@@ -4000,7 +3986,7 @@
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4013,26 +3999,22 @@
         <v>79</v>
       </c>
       <c r="I21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J21" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="J21" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="K21" t="s" s="2">
-        <v>111</v>
+        <v>210</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O21" t="s" s="2">
         <v>212</v>
       </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>79</v>
       </c>
@@ -4080,7 +4062,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4092,30 +4074,30 @@
         <v>79</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>79</v>
+        <v>213</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>193</v>
+        <v>214</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>79</v>
+        <v>215</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>79</v>
+        <v>216</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>79</v>
+        <v>217</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4123,30 +4105,32 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>215</v>
+        <v>170</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>79</v>
@@ -4171,13 +4155,13 @@
         <v>79</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>79</v>
+        <v>222</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>79</v>
+        <v>223</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>79</v>
+        <v>224</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>79</v>
@@ -4195,13 +4179,13 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>79</v>
@@ -4210,27 +4194,27 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4238,7 +4222,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>90</v>
@@ -4247,23 +4231,21 @@
         <v>79</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>170</v>
+        <v>231</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>79</v>
@@ -4288,13 +4270,11 @@
         <v>79</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="Y23" t="s" s="2">
-        <v>228</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>79</v>
@@ -4312,10 +4292,10 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>90</v>
@@ -4327,19 +4307,19 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>230</v>
+        <v>79</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>231</v>
+        <v>108</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>232</v>
+        <v>79</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>233</v>
+        <v>79</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>234</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24">
@@ -4358,7 +4338,7 @@
         <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>79</v>
@@ -4370,13 +4350,13 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4407,7 +4387,7 @@
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>79</v>
@@ -4431,7 +4411,7 @@
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>79</v>
@@ -4443,10 +4423,10 @@
         <v>79</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>108</v>
+        <v>239</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>79</v>
+        <v>240</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>79</v>
@@ -4457,10 +4437,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4483,15 +4463,17 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>79</v>
@@ -4520,7 +4502,7 @@
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>79</v>
@@ -4538,7 +4520,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4553,13 +4535,13 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>79</v>
+        <v>246</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>245</v>
+        <v>79</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>79</v>
@@ -4570,10 +4552,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4596,17 +4578,15 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N26" t="s" s="2">
         <v>249</v>
       </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>79</v>
@@ -4631,7 +4611,7 @@
         <v>79</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>160</v>
+        <v>222</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
@@ -4653,7 +4633,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4668,16 +4648,16 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="AL26" t="s" s="2">
-        <v>244</v>
-      </c>
       <c r="AM26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>79</v>
+        <v>252</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>79</v>
@@ -4685,10 +4665,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4699,7 +4679,7 @@
         <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>79</v>
@@ -4711,13 +4691,13 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4744,11 +4724,11 @@
         <v>79</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>227</v>
+        <v>174</v>
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>79</v>
@@ -4766,13 +4746,13 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>79</v>
@@ -4784,24 +4764,24 @@
         <v>79</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>79</v>
+        <v>258</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>257</v>
+        <v>79</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>79</v>
+        <v>259</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4812,7 +4792,7 @@
         <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>79</v>
@@ -4824,13 +4804,13 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4859,9 +4839,11 @@
       <c r="X28" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="Y28" s="2"/>
+      <c r="Y28" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="Z28" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>79</v>
@@ -4879,13 +4861,13 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>79</v>
@@ -4894,27 +4876,27 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>79</v>
+        <v>265</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>263</v>
+        <v>79</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4934,16 +4916,16 @@
         <v>79</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>236</v>
+        <v>269</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4970,31 +4952,31 @@
         <v>79</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="Y29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5009,10 +4991,10 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>79</v>
@@ -5021,15 +5003,15 @@
         <v>79</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>272</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5040,7 +5022,7 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>79</v>
@@ -5052,15 +5034,17 @@
         <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>79</v>
@@ -5109,13 +5093,13 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>79</v>
@@ -5124,27 +5108,27 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>79</v>
+        <v>281</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>79</v>
+        <v>252</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>79</v>
+        <v>282</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5167,17 +5151,15 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>280</v>
+        <v>104</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>283</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>79</v>
@@ -5226,7 +5208,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5241,27 +5223,27 @@
         <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>284</v>
+        <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>257</v>
+        <v>79</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5272,7 +5254,7 @@
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>79</v>
@@ -5284,13 +5266,13 @@
         <v>79</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>104</v>
+        <v>290</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5341,13 +5323,13 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>79</v>
@@ -5356,27 +5338,27 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>79</v>
+        <v>293</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>79</v>
+        <v>296</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>293</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5387,7 +5369,7 @@
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>79</v>
@@ -5396,16 +5378,16 @@
         <v>79</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>295</v>
+        <v>126</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5456,13 +5438,13 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>79</v>
@@ -5471,27 +5453,27 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>79</v>
+        <v>304</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5517,10 +5499,10 @@
         <v>126</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5571,7 +5553,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5586,27 +5568,27 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5626,16 +5608,16 @@
         <v>79</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>126</v>
+        <v>313</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5686,7 +5668,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5701,27 +5683,27 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>315</v>
+        <v>79</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>316</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5732,7 +5714,7 @@
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>79</v>
@@ -5744,13 +5726,13 @@
         <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5801,13 +5783,13 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>79</v>
@@ -5816,13 +5798,13 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>305</v>
+        <v>79</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>322</v>
+        <v>79</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>79</v>
@@ -5847,7 +5829,7 @@
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>79</v>
@@ -5867,7 +5849,9 @@
       <c r="M37" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="N37" s="2"/>
+      <c r="N37" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>79</v>
@@ -5922,7 +5906,7 @@
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>79</v>
@@ -5931,13 +5915,13 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>79</v>
+        <v>328</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>79</v>
+        <v>330</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>79</v>
@@ -5948,10 +5932,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5974,16 +5958,16 @@
         <v>79</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>329</v>
+        <v>104</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6033,7 +6017,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6048,27 +6032,27 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>79</v>
+        <v>288</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6094,14 +6078,12 @@
         <v>104</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>339</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>79</v>
@@ -6150,7 +6132,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6165,38 +6147,38 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>340</v>
+        <v>79</v>
       </c>
       <c r="AL39" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="AM39" t="s" s="2">
-        <v>342</v>
-      </c>
       <c r="AN39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>79</v>
+        <v>343</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>79</v>
@@ -6208,13 +6190,13 @@
         <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>104</v>
+        <v>344</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6265,13 +6247,13 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>79</v>
@@ -6280,35 +6262,35 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>79</v>
+        <v>347</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>346</v>
+        <v>79</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>293</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>348</v>
+        <v>79</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>81</v>
@@ -6323,13 +6305,13 @@
         <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6380,10 +6362,10 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>81</v>
@@ -6392,30 +6374,30 @@
         <v>79</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>102</v>
+        <v>353</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>79</v>
+        <v>356</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>79</v>
+        <v>357</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6423,11 +6405,11 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G42" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="G42" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="H42" t="s" s="2">
         <v>79</v>
       </c>
@@ -6438,13 +6420,13 @@
         <v>79</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>355</v>
+        <v>104</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>356</v>
+        <v>105</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>357</v>
+        <v>106</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6495,53 +6477,53 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>354</v>
+        <v>107</v>
       </c>
       <c r="AG42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH42" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="AH42" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>358</v>
+        <v>79</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>359</v>
+        <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>360</v>
+        <v>108</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>361</v>
+        <v>79</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>362</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>79</v>
@@ -6553,15 +6535,17 @@
         <v>79</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>79</v>
@@ -6610,19 +6594,19 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>79</v>
@@ -6642,14 +6626,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>110</v>
+        <v>361</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6662,24 +6646,26 @@
         <v>79</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
         <v>111</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>112</v>
+        <v>362</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>113</v>
+        <v>363</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="O44" s="2"/>
+      <c r="O44" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
       </c>
@@ -6727,7 +6713,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>118</v>
+        <v>364</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6745,7 +6731,7 @@
         <v>79</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>108</v>
+        <v>193</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>79</v>
@@ -6766,7 +6752,7 @@
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>366</v>
+        <v>79</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6779,26 +6765,24 @@
         <v>79</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J45" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>111</v>
+        <v>231</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="N45" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>212</v>
-      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>79</v>
       </c>
@@ -6822,13 +6806,13 @@
         <v>79</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>79</v>
+        <v>369</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>79</v>
+        <v>370</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>79</v>
@@ -6846,7 +6830,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6858,30 +6842,30 @@
         <v>79</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>193</v>
+        <v>371</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>79</v>
+        <v>372</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6892,7 +6876,7 @@
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>79</v>
@@ -6904,17 +6888,15 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>236</v>
+        <v>374</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>373</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>79</v>
@@ -6939,13 +6921,13 @@
         <v>79</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>152</v>
+        <v>79</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>374</v>
+        <v>79</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>375</v>
+        <v>79</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>79</v>
@@ -6963,13 +6945,13 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>79</v>
@@ -6981,24 +6963,24 @@
         <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>108</v>
+        <v>378</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>79</v>
+        <v>379</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7021,13 +7003,13 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>379</v>
+        <v>170</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7054,13 +7036,13 @@
         <v>79</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>79</v>
+        <v>222</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>79</v>
+        <v>384</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>79</v>
+        <v>385</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>79</v>
@@ -7078,7 +7060,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7096,24 +7078,24 @@
         <v>79</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>384</v>
+        <v>79</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>385</v>
+        <v>79</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7121,7 +7103,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>90</v>
@@ -7139,10 +7121,10 @@
         <v>170</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7169,13 +7151,13 @@
         <v>79</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>79</v>
@@ -7193,10 +7175,10 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>90</v>
@@ -7211,24 +7193,24 @@
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>79</v>
+        <v>395</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7236,7 +7218,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>90</v>
@@ -7248,16 +7230,16 @@
         <v>79</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>170</v>
+        <v>397</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7284,34 +7266,34 @@
         <v>79</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>227</v>
+        <v>79</v>
       </c>
       <c r="Y49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF49" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="Z49" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>393</v>
-      </c>
       <c r="AG49" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>90</v>
@@ -7326,24 +7308,24 @@
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>398</v>
+        <v>108</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>399</v>
+        <v>79</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>400</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7354,7 +7336,7 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>79</v>
@@ -7366,15 +7348,17 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="M50" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>79</v>
@@ -7423,13 +7407,13 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>79</v>
@@ -7438,10 +7422,10 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>79</v>
+        <v>300</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>108</v>
+        <v>404</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
@@ -7450,124 +7434,7 @@
         <v>79</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="C51" s="2"/>
-      <c r="D51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E51" s="2"/>
-      <c r="F51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G51" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K51" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="O51" s="2"/>
-      <c r="P51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q51" s="2"/>
-      <c r="R51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>410</v>
       </c>
     </row>
   </sheetData>

--- a/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-appointment-fr.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1865" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1865" uniqueCount="407">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>1.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T09:27:09+00:00</t>
+    <t>2026-04-10T11:37:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -442,7 +442,7 @@
     <t>Appointment.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -471,6 +471,9 @@
     <t>fr-canonical</t>
   </si>
   <si>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-appointment|2.2.0</t>
+  </si>
+  <si>
     <t>Appointment.meta.security</t>
   </si>
   <si>
@@ -493,7 +496,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -517,7 +520,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -560,7 +563,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -636,14 +639,15 @@
     <t>appointmentOperator</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-appointment-operator}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-appointment-operator|2.2.0}
 </t>
   </si>
   <si>
     <t>FR Core Appointment Operator Extension</t>
   </si>
   <si>
-    <t>This extension adds the element appointmentOperator to the Appointment resource (operator of creation/update/cancel of the appointment | Cette extension ajoute l'élément appointmentOperator à la ressource Appointment (opérateur de création/modification/annulation du RDV)</t>
+    <t>Cette extension ajoute l'élément appointmentOperator à la ressource Appointment (opérateur de création/modification/annulation du RDV). 
+This extension adds the element appointmentOperator to the Appointment resource (operator of creation/update/cancel of the appointment</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -744,7 +748,7 @@
     <t>The coded reason for the appointment being cancelled. This is often used in reporting/billing/futher processing to determine if further actions are required, or specific fees apply.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/appointment-cancellation-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/appointment-cancellation-reason|4.0.1</t>
   </si>
   <si>
     <t>Appointment.serviceCategory</t>
@@ -756,7 +760,7 @@
     <t>A broad categorization of the service that is to be performed during this appointment.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-category</t>
+    <t>http://hl7.org/fhir/ValueSet/service-category|4.0.1</t>
   </si>
   <si>
     <t>n/a, might be inferred from the ServiceDeliveryLocation</t>
@@ -777,7 +781,7 @@
     <t>For a provider to provider appointment the code "FOLLOWUP" may be appropriate, as this is expected to be discussing some patient that was seen in the past.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-type</t>
+    <t>http://hl7.org/fhir/ValueSet/service-type|4.0.1</t>
   </si>
   <si>
     <t>Request.code</t>
@@ -792,7 +796,7 @@
     <t>The specialty of a practitioner that would be required to perform the service requested in this appointment.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-specialty</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-specialty|2.2.0</t>
   </si>
   <si>
     <t>.performer.AssignedPerson.code</t>
@@ -810,7 +814,7 @@
     <t>The style of appointment or patient that has been booked in the slot (not service type).</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0276</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0276|3.0.0</t>
   </si>
   <si>
     <t>.code</t>
@@ -834,7 +838,7 @@
     <t>The Reason for the appointment to take place.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-reason|4.0.1</t>
   </si>
   <si>
     <t>Request.reasonCode</t>
@@ -849,7 +853,7 @@
     <t>Appointment.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Procedure|Observation|ImmunizationRecommendation)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Procedure|4.0.1|Observation|4.0.1|ImmunizationRecommendation|4.0.1)
 </t>
   </si>
   <si>
@@ -916,7 +920,7 @@
     <t>Appointment.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1005,7 +1009,7 @@
     <t>Appointment.slot</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-slot)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-slot|2.2.0)
 </t>
   </si>
   <si>
@@ -1085,7 +1089,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest)
+    <t xml:space="preserve">Reference(ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -1172,7 +1176,7 @@
     <t>Role of participant in encounter.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-participant-type</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-participant-type|4.0.1</t>
   </si>
   <si>
     <t>(performer | reusableDevice | subject | location).@typeCode</t>
@@ -1184,7 +1188,7 @@
     <t>Appointment.participant.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-ins|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-ins|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-healthcare-service)
 </t>
   </si>
   <si>
@@ -1603,7 +1607,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="156.30078125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="212.09375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1618,7 +1622,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.66796875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="57.19921875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -2857,7 +2861,7 @@
         <v>79</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>33</v>
+        <v>147</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>79</v>
@@ -2928,10 +2932,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2954,16 +2958,16 @@
         <v>91</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2989,13 +2993,13 @@
         <v>79</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>79</v>
@@ -3013,7 +3017,7 @@
         <v>79</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3045,10 +3049,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3071,16 +3075,16 @@
         <v>91</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3106,13 +3110,13 @@
         <v>79</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>79</v>
@@ -3130,7 +3134,7 @@
         <v>79</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3162,10 +3166,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3191,13 +3195,13 @@
         <v>132</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3247,7 +3251,7 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3279,10 +3283,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3305,16 +3309,16 @@
         <v>79</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3340,13 +3344,13 @@
         <v>79</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>79</v>
@@ -3364,7 +3368,7 @@
         <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3396,14 +3400,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3422,16 +3426,16 @@
         <v>79</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3481,7 +3485,7 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3499,7 +3503,7 @@
         <v>79</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>79</v>
@@ -3513,14 +3517,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3539,16 +3543,16 @@
         <v>79</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3598,7 +3602,7 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3616,7 +3620,7 @@
         <v>79</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>79</v>
@@ -3630,10 +3634,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3659,10 +3663,10 @@
         <v>111</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3711,7 +3715,7 @@
         <v>117</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3743,13 +3747,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>79</v>
@@ -3771,13 +3775,13 @@
         <v>79</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3828,7 +3832,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -3837,7 +3841,7 @@
         <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>119</v>
@@ -3860,10 +3864,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3889,16 +3893,16 @@
         <v>111</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>79</v>
@@ -3947,7 +3951,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -3965,7 +3969,7 @@
         <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>79</v>
@@ -3979,10 +3983,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4005,13 +4009,13 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4062,7 +4066,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4077,27 +4081,27 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4120,16 +4124,16 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4155,13 +4159,13 @@
         <v>79</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>79</v>
@@ -4179,7 +4183,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>90</v>
@@ -4194,27 +4198,27 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4237,13 +4241,13 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4270,11 +4274,11 @@
         <v>79</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>79</v>
@@ -4292,7 +4296,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4324,10 +4328,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4350,13 +4354,13 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4383,11 +4387,11 @@
         <v>79</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>79</v>
@@ -4405,7 +4409,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4423,10 +4427,10 @@
         <v>79</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>79</v>
@@ -4437,10 +4441,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4463,16 +4467,16 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4498,11 +4502,11 @@
         <v>79</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>79</v>
@@ -4520,7 +4524,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4535,10 +4539,10 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>79</v>
@@ -4552,10 +4556,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4578,13 +4582,13 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4611,11 +4615,11 @@
         <v>79</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>79</v>
@@ -4633,7 +4637,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4651,13 +4655,13 @@
         <v>79</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>79</v>
@@ -4665,10 +4669,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4691,13 +4695,13 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4724,11 +4728,11 @@
         <v>79</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>79</v>
@@ -4746,7 +4750,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4764,24 +4768,24 @@
         <v>79</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4804,13 +4808,13 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4837,13 +4841,13 @@
         <v>79</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>79</v>
@@ -4861,7 +4865,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -4876,10 +4880,10 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>79</v>
@@ -4888,15 +4892,15 @@
         <v>79</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4919,13 +4923,13 @@
         <v>79</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4976,7 +4980,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -4991,10 +4995,10 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>79</v>
@@ -5008,10 +5012,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5034,16 +5038,16 @@
         <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5093,7 +5097,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5108,27 +5112,27 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5154,10 +5158,10 @@
         <v>104</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5208,7 +5212,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5226,24 +5230,24 @@
         <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5266,13 +5270,13 @@
         <v>79</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5323,7 +5327,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5338,16 +5342,16 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>79</v>
@@ -5355,10 +5359,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5384,10 +5388,10 @@
         <v>126</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5438,7 +5442,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5453,27 +5457,27 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5499,10 +5503,10 @@
         <v>126</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5553,7 +5557,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5568,27 +5572,27 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5611,13 +5615,13 @@
         <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5668,7 +5672,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5683,13 +5687,13 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>79</v>
@@ -5700,10 +5704,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5726,13 +5730,13 @@
         <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5783,7 +5787,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5801,7 +5805,7 @@
         <v>79</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>79</v>
@@ -5815,10 +5819,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5841,16 +5845,16 @@
         <v>79</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5900,7 +5904,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5915,13 +5919,13 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>79</v>
@@ -5932,10 +5936,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5961,13 +5965,13 @@
         <v>104</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6017,7 +6021,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6032,27 +6036,27 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6078,10 +6082,10 @@
         <v>104</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6132,7 +6136,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6150,28 +6154,28 @@
         <v>79</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6190,13 +6194,13 @@
         <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6247,7 +6251,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6262,10 +6266,10 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>79</v>
@@ -6279,10 +6283,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6305,13 +6309,13 @@
         <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6362,7 +6366,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>90</v>
@@ -6374,30 +6378,30 @@
         <v>79</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6509,10 +6513,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6626,14 +6630,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6655,16 +6659,16 @@
         <v>111</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -6713,7 +6717,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6731,7 +6735,7 @@
         <v>79</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>79</v>
@@ -6745,10 +6749,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6771,16 +6775,16 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6806,13 +6810,13 @@
         <v>79</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>79</v>
@@ -6830,7 +6834,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6848,7 +6852,7 @@
         <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>108</v>
@@ -6857,15 +6861,15 @@
         <v>79</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6888,13 +6892,13 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6945,7 +6949,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6963,24 +6967,24 @@
         <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7003,13 +7007,13 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7036,13 +7040,13 @@
         <v>79</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>79</v>
@@ -7060,7 +7064,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7078,10 +7082,10 @@
         <v>79</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>79</v>
@@ -7092,10 +7096,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7118,13 +7122,13 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7151,13 +7155,13 @@
         <v>79</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>79</v>
@@ -7175,7 +7179,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>90</v>
@@ -7193,24 +7197,24 @@
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7233,13 +7237,13 @@
         <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7290,7 +7294,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7322,10 +7326,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7348,16 +7352,16 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7407,7 +7411,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7422,10 +7426,10 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
@@ -7434,7 +7438,7 @@
         <v>79</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
   </sheetData>
